--- a/ecommerce-sales-analysis/excel/ecommerce_sales_analysis.xlsx
+++ b/ecommerce-sales-analysis/excel/ecommerce_sales_analysis.xlsx
@@ -2,21 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kavya\OneDrive\Desktop\ecommerce-sales-analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BAC9EF00-43B3-4344-BFF5-222AFD90C133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C12B1004-EDE1-4E10-951E-EB9D3CD6E1D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11970" yWindow="0" windowWidth="16485" windowHeight="15585" xr2:uid="{72824441-3ECF-42E4-BA03-BA94AA4EA19E}"/>
+    <workbookView xWindow="12135" yWindow="0" windowWidth="16050" windowHeight="15585" firstSheet="3" activeTab="4" xr2:uid="{72824441-3ECF-42E4-BA03-BA94AA4EA19E}"/>
   </bookViews>
   <sheets>
-    <sheet name="ecommerce_sales" sheetId="1" r:id="rId1"/>
-    <sheet name="Formula Analysis" sheetId="2" r:id="rId2"/>
+    <sheet name="Sales_By_City" sheetId="5" r:id="rId1"/>
+    <sheet name="Sales_by_Channel" sheetId="6" r:id="rId2"/>
+    <sheet name="ecommerce_sales" sheetId="1" r:id="rId3"/>
+    <sheet name="Formula Analysis" sheetId="2" r:id="rId4"/>
+    <sheet name="Dashboard" sheetId="3" r:id="rId5"/>
+    <sheet name="sheet" sheetId="4" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="5" r:id="rId7"/>
+  </pivotCaches>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -43,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="128">
   <si>
     <t>order_id</t>
   </si>
@@ -403,13 +421,40 @@
   </si>
   <si>
     <t>Net Sales per Item</t>
+  </si>
+  <si>
+    <t>E-Commerce Sales Dashboard</t>
+  </si>
+  <si>
+    <t>Total Net Sales</t>
+  </si>
+  <si>
+    <t>Top City</t>
+  </si>
+  <si>
+    <t>Top Category</t>
+  </si>
+  <si>
+    <t>Total Orders</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of net_sales_inr</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19">
+  <numFmts count="1">
+    <numFmt numFmtId="8" formatCode="&quot;₹&quot;\ #,##0.00;[Red]&quot;₹&quot;\ \-#,##0.00"/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -548,6 +593,14 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -891,10 +944,18 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -951,6 +1012,5200 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[ecommerce_sales_analysis.xlsx]Sales_By_City!PivotTable1</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Net Sales BY City</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sales_By_City!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sales_By_City!$A$2:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Alappuzha</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Kochi</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Kollam</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Kottayam</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Thiruvananthapuram</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Thrissur</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sales_By_City!$B$2:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>16749.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>28571.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>19907.05</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24844.300000000003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10731.3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>12227.25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E9FA-4B4F-A104-A558A4E248FB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1232239407"/>
+        <c:axId val="1166094031"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1232239407"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1166094031"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1166094031"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1232239407"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[ecommerce_sales_analysis.xlsx]Sales_by_Channel!PivotTable2</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Net Sales by Sales Channel</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sales_by_Channel!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sales_by_Channel!$A$2:$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Online</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Store</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sales_by_Channel!$B$2:$B$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>64408.749999999993</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>48621.750000000015</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2A67-44B8-9AAB-887D0D0EE679}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1344266783"/>
+        <c:axId val="1166146351"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1344266783"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1166146351"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1166146351"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1344266783"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[ecommerce_sales_analysis.xlsx]Sales_By_City!PivotTable1</c:name>
+    <c:fmtId val="6"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Net Sales by City</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sales_By_City!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sales_By_City!$A$2:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Alappuzha</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Kochi</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Kollam</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Kottayam</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Thiruvananthapuram</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Thrissur</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sales_By_City!$B$2:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>16749.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>28571.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>19907.05</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24844.300000000003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10731.3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>12227.25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E506-4414-998F-506B5D24E275}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1232239407"/>
+        <c:axId val="1166094031"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1232239407"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1166094031"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1166094031"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1232239407"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[ecommerce_sales_analysis.xlsx]Sales_by_Channel!PivotTable2</c:name>
+    <c:fmtId val="3"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Net Sales by Sales Channel</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sales_by_Channel!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sales_by_Channel!$A$2:$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Online</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Store</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sales_by_Channel!$B$2:$B$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>64408.749999999993</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>48621.750000000015</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-045C-4E1F-BEB1-9CB70AB25B32}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1344266783"/>
+        <c:axId val="1166146351"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1344266783"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1166146351"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1166146351"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1344266783"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5E17394-D243-2E98-ED41-86FBE9C5C28C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0D60ECA-7107-7C78-8BC4-5B7C43B6916B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52E6CF73-FBF8-4C56-9A9D-BD1574C9614B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{159AC883-D88E-4ED5-BABC-0D60EDC86203}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="kavya" refreshedDate="46311.85090972222" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="40" xr:uid="{3343A794-FA5C-4BD1-9B93-CD8753B1273E}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:Q41" sheet="ecommerce_sales"/>
+  </cacheSource>
+  <cacheFields count="17">
+    <cacheField name="order_id" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="order_date" numFmtId="14">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-01-03T00:00:00" maxDate="2026-06-23T00:00:00"/>
+    </cacheField>
+    <cacheField name="customer_id" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="city" numFmtId="0">
+      <sharedItems count="6">
+        <s v="Kochi"/>
+        <s v="Kollam"/>
+        <s v="Thiruvananthapuram"/>
+        <s v="Alappuzha"/>
+        <s v="Thrissur"/>
+        <s v="Kottayam"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="category" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="product" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="quantity" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="5"/>
+    </cacheField>
+    <cacheField name="unit_price_inr" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="399" maxValue="6499"/>
+    </cacheField>
+    <cacheField name="discount_rate" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="0.1"/>
+    </cacheField>
+    <cacheField name="sales_channel" numFmtId="0">
+      <sharedItems count="2">
+        <s v="Online"/>
+        <s v="Store"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="gross_sales_inr" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="798" maxValue="12998"/>
+    </cacheField>
+    <cacheField name="discount_amount_inr" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="1299.8"/>
+    </cacheField>
+    <cacheField name="net_sales_inr" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="798" maxValue="11698.2"/>
+    </cacheField>
+    <cacheField name="Sales Level" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Priority Order" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Review Flag" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Net Sales per Item" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="359.1" maxValue="6499"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="40">
+  <r>
+    <s v="ORD1001"/>
+    <d v="2026-01-03T00:00:00"/>
+    <s v="C001"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <s v="Wireless Mouse"/>
+    <n v="2"/>
+    <n v="799"/>
+    <n v="0"/>
+    <x v="0"/>
+    <n v="1598"/>
+    <n v="0"/>
+    <n v="1598"/>
+    <s v="Medium"/>
+    <s v="Priority"/>
+    <s v="Normal"/>
+    <n v="799"/>
+  </r>
+  <r>
+    <s v="ORD1002"/>
+    <d v="2026-01-04T00:00:00"/>
+    <s v="C002"/>
+    <x v="1"/>
+    <s v="Home"/>
+    <s v="Desk Lamp"/>
+    <n v="1"/>
+    <n v="1299"/>
+    <n v="0.05"/>
+    <x v="0"/>
+    <n v="1299"/>
+    <n v="64.95"/>
+    <n v="1234.05"/>
+    <s v="Low"/>
+    <s v="Normal"/>
+    <s v="Normal"/>
+    <n v="1234.05"/>
+  </r>
+  <r>
+    <s v="ORD1003"/>
+    <d v="2026-01-06T00:00:00"/>
+    <s v="C003"/>
+    <x v="2"/>
+    <s v="Fashion"/>
+    <s v="Backpack"/>
+    <n v="1"/>
+    <n v="1499"/>
+    <n v="0.1"/>
+    <x v="1"/>
+    <n v="1499"/>
+    <n v="149.9"/>
+    <n v="1349.1"/>
+    <s v="Low"/>
+    <s v="Normal"/>
+    <s v="Review"/>
+    <n v="1349.1"/>
+  </r>
+  <r>
+    <s v="ORD1004"/>
+    <d v="2026-01-10T00:00:00"/>
+    <s v="C004"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <s v="Keyboard"/>
+    <n v="1"/>
+    <n v="1899"/>
+    <n v="0"/>
+    <x v="0"/>
+    <n v="1899"/>
+    <n v="0"/>
+    <n v="1899"/>
+    <s v="Medium"/>
+    <s v="Priority"/>
+    <s v="Normal"/>
+    <n v="1899"/>
+  </r>
+  <r>
+    <s v="ORD1005"/>
+    <d v="2026-01-12T00:00:00"/>
+    <s v="C005"/>
+    <x v="3"/>
+    <s v="Home"/>
+    <s v="Water Bottle"/>
+    <n v="3"/>
+    <n v="399"/>
+    <n v="0"/>
+    <x v="1"/>
+    <n v="1197"/>
+    <n v="0"/>
+    <n v="1197"/>
+    <s v="Low"/>
+    <s v="Normal"/>
+    <s v="Review"/>
+    <n v="399"/>
+  </r>
+  <r>
+    <s v="ORD1006"/>
+    <d v="2026-01-16T00:00:00"/>
+    <s v="C006"/>
+    <x v="1"/>
+    <s v="Fashion"/>
+    <s v="T-shirt"/>
+    <n v="2"/>
+    <n v="599"/>
+    <n v="0.05"/>
+    <x v="0"/>
+    <n v="1198"/>
+    <n v="59.9"/>
+    <n v="1138.0999999999999"/>
+    <s v="Low"/>
+    <s v="Normal"/>
+    <s v="Normal"/>
+    <n v="569.04999999999995"/>
+  </r>
+  <r>
+    <s v="ORD1007"/>
+    <d v="2026-01-20T00:00:00"/>
+    <s v="C001"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <s v="USB-C Hub"/>
+    <n v="1"/>
+    <n v="2199"/>
+    <n v="0.1"/>
+    <x v="0"/>
+    <n v="2199"/>
+    <n v="219.9"/>
+    <n v="1979.1"/>
+    <s v="Medium"/>
+    <s v="Priority"/>
+    <s v="Normal"/>
+    <n v="1979.1"/>
+  </r>
+  <r>
+    <s v="ORD1008"/>
+    <d v="2026-01-25T00:00:00"/>
+    <s v="C007"/>
+    <x v="4"/>
+    <s v="Home"/>
+    <s v="Office Chair"/>
+    <n v="1"/>
+    <n v="6499"/>
+    <n v="0.05"/>
+    <x v="1"/>
+    <n v="6499"/>
+    <n v="324.95"/>
+    <n v="6174.05"/>
+    <s v="High"/>
+    <s v="Normal"/>
+    <s v="Review"/>
+    <n v="6174.05"/>
+  </r>
+  <r>
+    <s v="ORD1009"/>
+    <d v="2026-02-02T00:00:00"/>
+    <s v="C008"/>
+    <x v="0"/>
+    <s v="Fashion"/>
+    <s v="Sneakers"/>
+    <n v="1"/>
+    <n v="2999"/>
+    <n v="0"/>
+    <x v="0"/>
+    <n v="2999"/>
+    <n v="0"/>
+    <n v="2999"/>
+    <s v="Medium"/>
+    <s v="Priority"/>
+    <s v="Normal"/>
+    <n v="2999"/>
+  </r>
+  <r>
+    <s v="ORD1010"/>
+    <d v="2026-02-05T00:00:00"/>
+    <s v="C009"/>
+    <x v="5"/>
+    <s v="Electronics"/>
+    <s v="Headphones"/>
+    <n v="1"/>
+    <n v="2499"/>
+    <n v="0.1"/>
+    <x v="0"/>
+    <n v="2499"/>
+    <n v="249.9"/>
+    <n v="2249.1"/>
+    <s v="Medium"/>
+    <s v="Priority"/>
+    <s v="Normal"/>
+    <n v="2249.1"/>
+  </r>
+  <r>
+    <s v="ORD1011"/>
+    <d v="2026-02-08T00:00:00"/>
+    <s v="C010"/>
+    <x v="3"/>
+    <s v="Home"/>
+    <s v="Desk Lamp"/>
+    <n v="2"/>
+    <n v="1299"/>
+    <n v="0"/>
+    <x v="1"/>
+    <n v="2598"/>
+    <n v="0"/>
+    <n v="2598"/>
+    <s v="Medium"/>
+    <s v="Normal"/>
+    <s v="Review"/>
+    <n v="1299"/>
+  </r>
+  <r>
+    <s v="ORD1012"/>
+    <d v="2026-02-11T00:00:00"/>
+    <s v="C003"/>
+    <x v="2"/>
+    <s v="Fashion"/>
+    <s v="Backpack"/>
+    <n v="2"/>
+    <n v="1499"/>
+    <n v="0.05"/>
+    <x v="0"/>
+    <n v="2998"/>
+    <n v="149.9"/>
+    <n v="2848.1"/>
+    <s v="Medium"/>
+    <s v="Priority"/>
+    <s v="Normal"/>
+    <n v="1424.05"/>
+  </r>
+  <r>
+    <s v="ORD1013"/>
+    <d v="2026-02-14T00:00:00"/>
+    <s v="C011"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <s v="Wireless Mouse"/>
+    <n v="1"/>
+    <n v="799"/>
+    <n v="0"/>
+    <x v="1"/>
+    <n v="799"/>
+    <n v="0"/>
+    <n v="799"/>
+    <s v="Low"/>
+    <s v="Normal"/>
+    <s v="Review"/>
+    <n v="799"/>
+  </r>
+  <r>
+    <s v="ORD1014"/>
+    <d v="2026-02-18T00:00:00"/>
+    <s v="C012"/>
+    <x v="1"/>
+    <s v="Home"/>
+    <s v="Water Bottle"/>
+    <n v="4"/>
+    <n v="399"/>
+    <n v="0.1"/>
+    <x v="0"/>
+    <n v="1596"/>
+    <n v="159.6"/>
+    <n v="1436.4"/>
+    <s v="Low"/>
+    <s v="Normal"/>
+    <s v="Normal"/>
+    <n v="359.1"/>
+  </r>
+  <r>
+    <s v="ORD1015"/>
+    <d v="2026-02-22T00:00:00"/>
+    <s v="C013"/>
+    <x v="4"/>
+    <s v="Fashion"/>
+    <s v="T-shirt"/>
+    <n v="3"/>
+    <n v="599"/>
+    <n v="0"/>
+    <x v="0"/>
+    <n v="1797"/>
+    <n v="0"/>
+    <n v="1797"/>
+    <s v="Medium"/>
+    <s v="Priority"/>
+    <s v="Normal"/>
+    <n v="599"/>
+  </r>
+  <r>
+    <s v="ORD1016"/>
+    <d v="2026-03-01T00:00:00"/>
+    <s v="C014"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <s v="Keyboard"/>
+    <n v="2"/>
+    <n v="1899"/>
+    <n v="0.05"/>
+    <x v="0"/>
+    <n v="3798"/>
+    <n v="189.9"/>
+    <n v="3608.1"/>
+    <s v="High"/>
+    <s v="Priority"/>
+    <s v="Review"/>
+    <n v="1804.05"/>
+  </r>
+  <r>
+    <s v="ORD1017"/>
+    <d v="2026-03-04T00:00:00"/>
+    <s v="C015"/>
+    <x v="5"/>
+    <s v="Home"/>
+    <s v="Office Chair"/>
+    <n v="1"/>
+    <n v="6499"/>
+    <n v="0"/>
+    <x v="1"/>
+    <n v="6499"/>
+    <n v="0"/>
+    <n v="6499"/>
+    <s v="High"/>
+    <s v="Normal"/>
+    <s v="Review"/>
+    <n v="6499"/>
+  </r>
+  <r>
+    <s v="ORD1018"/>
+    <d v="2026-03-07T00:00:00"/>
+    <s v="C002"/>
+    <x v="1"/>
+    <s v="Fashion"/>
+    <s v="Sneakers"/>
+    <n v="1"/>
+    <n v="2999"/>
+    <n v="0.1"/>
+    <x v="0"/>
+    <n v="2999"/>
+    <n v="299.89999999999998"/>
+    <n v="2699.1"/>
+    <s v="Medium"/>
+    <s v="Priority"/>
+    <s v="Normal"/>
+    <n v="2699.1"/>
+  </r>
+  <r>
+    <s v="ORD1019"/>
+    <d v="2026-03-11T00:00:00"/>
+    <s v="C016"/>
+    <x v="3"/>
+    <s v="Electronics"/>
+    <s v="Headphones"/>
+    <n v="2"/>
+    <n v="2499"/>
+    <n v="0.05"/>
+    <x v="0"/>
+    <n v="4998"/>
+    <n v="249.9"/>
+    <n v="4748.1000000000004"/>
+    <s v="High"/>
+    <s v="Priority"/>
+    <s v="Review"/>
+    <n v="2374.0500000000002"/>
+  </r>
+  <r>
+    <s v="ORD1020"/>
+    <d v="2026-03-15T00:00:00"/>
+    <s v="C017"/>
+    <x v="0"/>
+    <s v="Home"/>
+    <s v="Desk Lamp"/>
+    <n v="1"/>
+    <n v="1299"/>
+    <n v="0"/>
+    <x v="1"/>
+    <n v="1299"/>
+    <n v="0"/>
+    <n v="1299"/>
+    <s v="Low"/>
+    <s v="Normal"/>
+    <s v="Review"/>
+    <n v="1299"/>
+  </r>
+  <r>
+    <s v="ORD1021"/>
+    <d v="2026-03-19T00:00:00"/>
+    <s v="C018"/>
+    <x v="2"/>
+    <s v="Fashion"/>
+    <s v="T-shirt"/>
+    <n v="2"/>
+    <n v="599"/>
+    <n v="0.05"/>
+    <x v="0"/>
+    <n v="1198"/>
+    <n v="59.9"/>
+    <n v="1138.0999999999999"/>
+    <s v="Low"/>
+    <s v="Normal"/>
+    <s v="Normal"/>
+    <n v="569.04999999999995"/>
+  </r>
+  <r>
+    <s v="ORD1022"/>
+    <d v="2026-03-23T00:00:00"/>
+    <s v="C005"/>
+    <x v="3"/>
+    <s v="Home"/>
+    <s v="Water Bottle"/>
+    <n v="2"/>
+    <n v="399"/>
+    <n v="0"/>
+    <x v="0"/>
+    <n v="798"/>
+    <n v="0"/>
+    <n v="798"/>
+    <s v="Low"/>
+    <s v="Normal"/>
+    <s v="Normal"/>
+    <n v="399"/>
+  </r>
+  <r>
+    <s v="ORD1023"/>
+    <d v="2026-03-26T00:00:00"/>
+    <s v="C019"/>
+    <x v="1"/>
+    <s v="Electronics"/>
+    <s v="USB-C Hub"/>
+    <n v="1"/>
+    <n v="2199"/>
+    <n v="0"/>
+    <x v="1"/>
+    <n v="2199"/>
+    <n v="0"/>
+    <n v="2199"/>
+    <s v="Medium"/>
+    <s v="Normal"/>
+    <s v="Review"/>
+    <n v="2199"/>
+  </r>
+  <r>
+    <s v="ORD1024"/>
+    <d v="2026-03-29T00:00:00"/>
+    <s v="C020"/>
+    <x v="4"/>
+    <s v="Fashion"/>
+    <s v="Backpack"/>
+    <n v="1"/>
+    <n v="1499"/>
+    <n v="0.1"/>
+    <x v="0"/>
+    <n v="1499"/>
+    <n v="149.9"/>
+    <n v="1349.1"/>
+    <s v="Low"/>
+    <s v="Normal"/>
+    <s v="Normal"/>
+    <n v="1349.1"/>
+  </r>
+  <r>
+    <s v="ORD1025"/>
+    <d v="2026-04-02T00:00:00"/>
+    <s v="C021"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <s v="Headphones"/>
+    <n v="1"/>
+    <n v="2499"/>
+    <n v="0"/>
+    <x v="0"/>
+    <n v="2499"/>
+    <n v="0"/>
+    <n v="2499"/>
+    <s v="Medium"/>
+    <s v="Priority"/>
+    <s v="Normal"/>
+    <n v="2499"/>
+  </r>
+  <r>
+    <s v="ORD1026"/>
+    <d v="2026-04-06T00:00:00"/>
+    <s v="C022"/>
+    <x v="5"/>
+    <s v="Home"/>
+    <s v="Office Chair"/>
+    <n v="2"/>
+    <n v="6499"/>
+    <n v="0.1"/>
+    <x v="1"/>
+    <n v="12998"/>
+    <n v="1299.8"/>
+    <n v="11698.2"/>
+    <s v="High"/>
+    <s v="Normal"/>
+    <s v="Review"/>
+    <n v="5849.1"/>
+  </r>
+  <r>
+    <s v="ORD1027"/>
+    <d v="2026-04-10T00:00:00"/>
+    <s v="C023"/>
+    <x v="1"/>
+    <s v="Fashion"/>
+    <s v="Sneakers"/>
+    <n v="2"/>
+    <n v="2999"/>
+    <n v="0.05"/>
+    <x v="0"/>
+    <n v="5998"/>
+    <n v="299.89999999999998"/>
+    <n v="5698.1"/>
+    <s v="High"/>
+    <s v="Priority"/>
+    <s v="Review"/>
+    <n v="2849.05"/>
+  </r>
+  <r>
+    <s v="ORD1028"/>
+    <d v="2026-04-13T00:00:00"/>
+    <s v="C024"/>
+    <x v="2"/>
+    <s v="Electronics"/>
+    <s v="Wireless Mouse"/>
+    <n v="3"/>
+    <n v="799"/>
+    <n v="0"/>
+    <x v="0"/>
+    <n v="2397"/>
+    <n v="0"/>
+    <n v="2397"/>
+    <s v="Medium"/>
+    <s v="Priority"/>
+    <s v="Normal"/>
+    <n v="799"/>
+  </r>
+  <r>
+    <s v="ORD1029"/>
+    <d v="2026-04-18T00:00:00"/>
+    <s v="C025"/>
+    <x v="3"/>
+    <s v="Home"/>
+    <s v="Desk Lamp"/>
+    <n v="1"/>
+    <n v="1299"/>
+    <n v="0.05"/>
+    <x v="1"/>
+    <n v="1299"/>
+    <n v="64.95"/>
+    <n v="1234.05"/>
+    <s v="Low"/>
+    <s v="Normal"/>
+    <s v="Review"/>
+    <n v="1234.05"/>
+  </r>
+  <r>
+    <s v="ORD1030"/>
+    <d v="2026-04-22T00:00:00"/>
+    <s v="C026"/>
+    <x v="0"/>
+    <s v="Fashion"/>
+    <s v="T-shirt"/>
+    <n v="4"/>
+    <n v="599"/>
+    <n v="0"/>
+    <x v="0"/>
+    <n v="2396"/>
+    <n v="0"/>
+    <n v="2396"/>
+    <s v="Medium"/>
+    <s v="Priority"/>
+    <s v="Normal"/>
+    <n v="599"/>
+  </r>
+  <r>
+    <s v="ORD1031"/>
+    <d v="2026-05-01T00:00:00"/>
+    <s v="C027"/>
+    <x v="4"/>
+    <s v="Electronics"/>
+    <s v="Keyboard"/>
+    <n v="1"/>
+    <n v="1899"/>
+    <n v="0.1"/>
+    <x v="0"/>
+    <n v="1899"/>
+    <n v="189.9"/>
+    <n v="1709.1"/>
+    <s v="Medium"/>
+    <s v="Priority"/>
+    <s v="Normal"/>
+    <n v="1709.1"/>
+  </r>
+  <r>
+    <s v="ORD1032"/>
+    <d v="2026-05-05T00:00:00"/>
+    <s v="C028"/>
+    <x v="1"/>
+    <s v="Home"/>
+    <s v="Water Bottle"/>
+    <n v="5"/>
+    <n v="399"/>
+    <n v="0"/>
+    <x v="1"/>
+    <n v="1995"/>
+    <n v="0"/>
+    <n v="1995"/>
+    <s v="Medium"/>
+    <s v="Normal"/>
+    <s v="Review"/>
+    <n v="399"/>
+  </r>
+  <r>
+    <s v="ORD1033"/>
+    <d v="2026-05-09T00:00:00"/>
+    <s v="C029"/>
+    <x v="0"/>
+    <s v="Fashion"/>
+    <s v="Backpack"/>
+    <n v="2"/>
+    <n v="1499"/>
+    <n v="0.05"/>
+    <x v="0"/>
+    <n v="2998"/>
+    <n v="149.9"/>
+    <n v="2848.1"/>
+    <s v="Medium"/>
+    <s v="Priority"/>
+    <s v="Normal"/>
+    <n v="1424.05"/>
+  </r>
+  <r>
+    <s v="ORD1034"/>
+    <d v="2026-05-14T00:00:00"/>
+    <s v="C030"/>
+    <x v="5"/>
+    <s v="Electronics"/>
+    <s v="USB-C Hub"/>
+    <n v="2"/>
+    <n v="2199"/>
+    <n v="0"/>
+    <x v="0"/>
+    <n v="4398"/>
+    <n v="0"/>
+    <n v="4398"/>
+    <s v="High"/>
+    <s v="Priority"/>
+    <s v="Review"/>
+    <n v="2199"/>
+  </r>
+  <r>
+    <s v="ORD1035"/>
+    <d v="2026-05-20T00:00:00"/>
+    <s v="C031"/>
+    <x v="3"/>
+    <s v="Home"/>
+    <s v="Office Chair"/>
+    <n v="1"/>
+    <n v="6499"/>
+    <n v="0.05"/>
+    <x v="1"/>
+    <n v="6499"/>
+    <n v="324.95"/>
+    <n v="6174.05"/>
+    <s v="High"/>
+    <s v="Normal"/>
+    <s v="Review"/>
+    <n v="6174.05"/>
+  </r>
+  <r>
+    <s v="ORD1036"/>
+    <d v="2026-06-02T00:00:00"/>
+    <s v="C032"/>
+    <x v="2"/>
+    <s v="Fashion"/>
+    <s v="Sneakers"/>
+    <n v="1"/>
+    <n v="2999"/>
+    <n v="0"/>
+    <x v="0"/>
+    <n v="2999"/>
+    <n v="0"/>
+    <n v="2999"/>
+    <s v="Medium"/>
+    <s v="Priority"/>
+    <s v="Normal"/>
+    <n v="2999"/>
+  </r>
+  <r>
+    <s v="ORD1037"/>
+    <d v="2026-06-06T00:00:00"/>
+    <s v="C001"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <s v="Headphones"/>
+    <n v="2"/>
+    <n v="2499"/>
+    <n v="0.05"/>
+    <x v="0"/>
+    <n v="4998"/>
+    <n v="249.9"/>
+    <n v="4748.1000000000004"/>
+    <s v="High"/>
+    <s v="Priority"/>
+    <s v="Review"/>
+    <n v="2374.0500000000002"/>
+  </r>
+  <r>
+    <s v="ORD1038"/>
+    <d v="2026-06-10T00:00:00"/>
+    <s v="C033"/>
+    <x v="1"/>
+    <s v="Home"/>
+    <s v="Desk Lamp"/>
+    <n v="3"/>
+    <n v="1299"/>
+    <n v="0.1"/>
+    <x v="1"/>
+    <n v="3897"/>
+    <n v="389.7"/>
+    <n v="3507.3"/>
+    <s v="High"/>
+    <s v="Normal"/>
+    <s v="Review"/>
+    <n v="1169.1000000000001"/>
+  </r>
+  <r>
+    <s v="ORD1039"/>
+    <d v="2026-06-16T00:00:00"/>
+    <s v="C034"/>
+    <x v="4"/>
+    <s v="Fashion"/>
+    <s v="T-shirt"/>
+    <n v="2"/>
+    <n v="599"/>
+    <n v="0"/>
+    <x v="0"/>
+    <n v="1198"/>
+    <n v="0"/>
+    <n v="1198"/>
+    <s v="Low"/>
+    <s v="Normal"/>
+    <s v="Normal"/>
+    <n v="599"/>
+  </r>
+  <r>
+    <s v="ORD1040"/>
+    <d v="2026-06-22T00:00:00"/>
+    <s v="C035"/>
+    <x v="0"/>
+    <s v="Electronics"/>
+    <s v="Keyboard"/>
+    <n v="1"/>
+    <n v="1899"/>
+    <n v="0"/>
+    <x v="1"/>
+    <n v="1899"/>
+    <n v="0"/>
+    <n v="1899"/>
+    <s v="Medium"/>
+    <s v="Normal"/>
+    <s v="Review"/>
+    <n v="1899"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D47370D9-942D-4F96-8738-1FB61D9ADF9D}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+  <location ref="A1:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="17">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of net_sales_inr" fld="12" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{180DD545-8778-4E9A-85D5-276819F3073D}" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="A1:B4" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="17">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="9"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of net_sales_inr" fld="12" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1249,6 +6504,131 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A5D7883-973F-41D1-B465-8BD63BCA6C2E}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="7">
+        <v>16749.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="7">
+        <v>28571.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="7">
+        <v>19907.05</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="7">
+        <v>24844.300000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="7">
+        <v>10731.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="7">
+        <v>12227.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B8" s="7">
+        <v>113030.50000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C259AF8-2824-45E9-80C7-D6031262A8D6}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="7">
+        <v>64408.749999999993</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="7">
+        <v>48621.750000000015</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" s="7">
+        <v>113030.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19DA01BB-A888-480F-94BC-F0F445410159}">
   <dimension ref="A1:Q41"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3598,7 +8978,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C19233F-10F2-4683-A529-B311A3D0EE4F}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3663,4 +9043,62 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D911969-74E7-4B71-95B3-6B2372F49237}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14.28515625" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="6" max="6" width="6.85546875" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="23.25">
+      <c r="A1" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="24.75" customHeight="1">
+      <c r="A3" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3" s="4">
+        <v>113030.5</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3">
+        <v>40</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CE41268-270E-4195-A3C1-E2F081CFE825}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>